--- a/Primer sequences.xlsx
+++ b/Primer sequences.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cornellprod-my.sharepoint.com/personal/maq28_cornell_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C62B6181-1AFC-4346-80EB-E2AD2F09E994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{B23FFB19-EB3E-41D4-8D15-A1280B44D631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{666A1AE3-36FE-40AA-A626-6779A169DBFD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1530" windowWidth="29040" windowHeight="15720" xr2:uid="{CC8F0C81-D8F2-4F11-B225-1E298F0294C1}"/>
+    <workbookView xWindow="2955" yWindow="3015" windowWidth="17280" windowHeight="10005" xr2:uid="{CC8F0C81-D8F2-4F11-B225-1E298F0294C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,30 +59,12 @@
     <t>CGAACAAAGTATCCCACCTCTTCCAC</t>
   </si>
   <si>
-    <t>OCBD1HEX</t>
-  </si>
-  <si>
-    <t>GAAGGTCGGAGTCAACGGATT GGATTGATACAACCATCTTCTACAG</t>
-  </si>
-  <si>
     <t>Active THCAS</t>
   </si>
   <si>
-    <t>OCBD1FAM</t>
-  </si>
-  <si>
-    <t>GAAGGTGACCAAGTTCATGCT GGATTGATACAACCATCTTCTACAA</t>
-  </si>
-  <si>
     <t>OCBD S355N Inactivation</t>
   </si>
   <si>
-    <t>OCBD1Com</t>
-  </si>
-  <si>
-    <t>TTTCCTTTTTAAAATTAGCAGTGTTAA</t>
-  </si>
-  <si>
     <t>Common Rev</t>
   </si>
   <si>
@@ -408,9 +390,6 @@
   </si>
   <si>
     <t>CBDAS P476S Inactivation</t>
-  </si>
-  <si>
-    <t>**BD/BT requires some optimization for Tm still. Use CT1.1 for better chromatogram clustering**</t>
   </si>
   <si>
     <t>CT1.1HEX</t>
@@ -618,6 +597,27 @@
   </si>
   <si>
     <t>Auto2</t>
+  </si>
+  <si>
+    <t>**CCP-2 requires some optimization for Tm still. Use CCP-1.1 for better chromatogram clustering**</t>
+  </si>
+  <si>
+    <t>GGGTATTAAAAAAACTGATTGCAAAGAATTT</t>
+  </si>
+  <si>
+    <t>OCBD2.1Com</t>
+  </si>
+  <si>
+    <t>OCBD2HEX</t>
+  </si>
+  <si>
+    <t>OCBD2FAM</t>
+  </si>
+  <si>
+    <t>GAAGGTCGGAGTCAACGGATT TTAGCAGTGTTAAAATTTACAACACCAC</t>
+  </si>
+  <si>
+    <t>GAAGGTGACCAAGTTCATGCT  TTAGCAGTGTTAAAATTTACAACACCAT</t>
   </si>
 </sst>
 </file>
@@ -1089,30 +1089,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1143,670 +1143,670 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C7" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C8" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>185</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>11</v>
+        <v>187</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>183</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C15" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C16" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C19" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C20" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C23" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C27" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C31" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C32" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F34" s="10" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C35" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="F35" s="10" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C36" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C39" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C40" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C43" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F43" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C44" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C47" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C48" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G50" s="1"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C51" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G51" s="1"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C52" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C55" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C56" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G58" s="1"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C59" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C60" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C63" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C64" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G64" s="1"/>
     </row>

--- a/Primer sequences.xlsx
+++ b/Primer sequences.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cornellprod-my.sharepoint.com/personal/maq28_cornell_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{B23FFB19-EB3E-41D4-8D15-A1280B44D631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{666A1AE3-36FE-40AA-A626-6779A169DBFD}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{B23FFB19-EB3E-41D4-8D15-A1280B44D631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C35C702-5211-4634-B85A-37A719753C5F}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="3015" windowWidth="17280" windowHeight="10005" xr2:uid="{CC8F0C81-D8F2-4F11-B225-1E298F0294C1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CC8F0C81-D8F2-4F11-B225-1E298F0294C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -404,9 +404,6 @@
     <t>CBDAS Specific FAM</t>
   </si>
   <si>
-    <t>CT1-haplotype pseudogene Specific HEX</t>
-  </si>
-  <si>
     <t>GAAGGTGACCAAGTTCATGCT ATTAGACTGGTTGCTGTCCCAAA</t>
   </si>
   <si>
@@ -618,6 +615,9 @@
   </si>
   <si>
     <t>GAAGGTGACCAAGTTCATGCT  TTAGCAGTGTTAAAATTTACAACACCAT</t>
+  </si>
+  <si>
+    <t>BT-haplotype pseudogene Specific HEX</t>
   </si>
 </sst>
 </file>
@@ -756,6 +756,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1089,30 +1093,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
@@ -1143,30 +1147,30 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>118</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>122</v>
+        <v>187</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1174,13 +1178,13 @@
         <v>119</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>121</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1188,27 +1192,27 @@
         <v>120</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -1216,38 +1220,38 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C11" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C12" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>114</v>
@@ -1270,7 +1274,7 @@
         <v>117</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1284,15 +1288,15 @@
         <v>26</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
@@ -1315,7 +1319,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1329,15 +1333,15 @@
         <v>9</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>18</v>
@@ -1349,7 +1353,7 @@
         <v>20</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -1376,15 +1380,15 @@
         <v>26</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>101</v>
@@ -1407,7 +1411,7 @@
         <v>104</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1421,12 +1425,12 @@
         <v>106</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>61</v>
@@ -1452,7 +1456,7 @@
         <v>83</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1466,12 +1470,12 @@
         <v>75</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>62</v>
@@ -1486,7 +1490,7 @@
         <v>96</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1500,7 +1504,7 @@
         <v>97</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1514,60 +1518,60 @@
         <v>75</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C39" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="E39" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C40" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="F40" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>58</v>
@@ -1593,10 +1597,10 @@
         <v>73</v>
       </c>
       <c r="F43" t="s">
+        <v>175</v>
+      </c>
+      <c r="I43" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -1610,12 +1614,12 @@
         <v>75</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>59</v>
@@ -1641,7 +1645,7 @@
         <v>74</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -1655,7 +1659,7 @@
         <v>75</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -1734,7 +1738,7 @@
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>43</v>
@@ -1773,7 +1777,7 @@
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>50</v>
